--- a/medford_insufflyatory.xlsx
+++ b/medford_insufflyatory.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Инсуффляторы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray, MGB — всего 6 позиций.</t>
+          <t>Инсуффляторы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray, MGB.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_insufflyatory.xlsx
+++ b/medford_insufflyatory.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать инсуффляторы для клиники?</t>
+          <t>Зачем нужен инсуффлятор в хирургии?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Страна производства, Производитель, Рабочая температура, Класс и тип безопасности). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Эндоскопический инсуффлятор подаёт углекислый газ в брюшную полость и создаёт рабочее пространство — пневмоперитонеум, необходимый для лапароскопических операций. Контролируемая подача газа поддерживает стабильное давление в полости, что обеспечивает хирургу обзор и доступ к тканям. Параметры подачи регулируются в зависимости от типа вмешательства.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Чем инсуффлятор отличается от откашливателя?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Это разные устройства. Эндоскопический (лапароскопический) инсуффлятор подаёт CO₂ в брюшную полость при операциях. Медицинский откашливатель (инсуффлятор-аспиратор) применяется для выведения мокроты из дыхательных путей. Несмотря на схожее название, задачи, конструкция и применение у них разные, и путать их при выборе не следует.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Что даёт функция подогрева газа?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Mindray, MGB. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Подогрев CO₂ уменьшает охлаждение тканей и снижает запотевание оптики во время операции, что особенно важно при длительных вмешательствах. Без подогрева холодный газ может остужать ткани и ухудшать обзор. Функция подогрева есть, например, у инсуффлятора Mindray HS-50F и оценивается исходя из продолжительности операций.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Какие режимы работы бывают у инсуффлятора?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Современные инсуффляторы поддерживают несколько режимов под разные задачи. Например, Mindray HS-50F работает во взрослом, детском, бариатрическом, забрюшинном и пользовательском режимах. Разные режимы отличаются параметрами подачи и давления, что позволяет адаптировать аппарат под возраст пациента и тип вмешательства.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Какой класс электробезопасности нужен?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Для операционной инсуффлятор должен соответствовать требованиям электробезопасности. Газовые инсуффляторы MGB ML-G и ML-GX относятся к классу I, тип BF. Класс защиты и тип рабочей части уточняют по паспорту конкретной модели — это условие безопасной эксплуатации и допуска аппарата в состав операционного оборудования.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1188,6 +1188,120 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Как подобрать инсуффлятор под стойку?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Инсуффлятор подбирают под профиль операций и совместимость с расходными газовыми магистралями и фильтрами. Отдельно учитывают доступность и стоимость расходников. Требуемые режимы, диапазон подачи и функции (подогрев, отведение газа) согласуют с видами вмешательств. Совместимость расходных материалов проверяют до покупки.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>insufflyatory</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Нужна ли регистрация Росздравнадзора?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Для применения в клинике инсуффлятор должен быть зарегистрированным медицинским изделием с действующим регистрационным удостоверением Росздравнадзора. Статус регистрации уточняют до покупки — это условие законной эксплуатации в лечебном учреждении и один из обязательных критериев при выборе аппарата для операционной.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>insufflyatory</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Какие расходники нужны для работы?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Для работы инсуффлятора нужны совместимые газовые магистрали и фильтры, а также источник CO₂. Тип и доступность расходников влияют на текущие затраты кабинета, поэтому их уточняют заранее. Использование совместимых расходных материалов по инструкции производителя обеспечивает корректную и безопасную подачу газа.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>insufflyatory</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2072,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Инсуффляторы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Mindray, MGB.</t>
+          <t>Инсуффляторы — аппараты для подачи углекислого газа (CO₂) в брюшную полость и создания рабочего пространства при лапароскопии. В категории представлены модели Mindray, Крыло (Россия) и MGB (Германия). Инсуффлятор Mindray HS-50F управляется сенсорным цветным экраном, поддерживает бариатрический, взрослый, детский и забрюшинный режимы, оснащён функциями подогрева и отведения газа, минимальная подача — 0,1 л/мин. Газовые инсуффляторы MGB ML-G и ML-GX относятся к классу безопасности I, тип BF.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2356,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Инсуффляторы: разделение сущностей</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2644,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое инсуффляторы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3300,239 +3414,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Инсуффляторы: разделение сущностей</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Тип аппарата</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Назначение</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Страна производства</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Производитель</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Рабочая температура</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Класс и тип безопасности</t>
+          <t>Отношение к категории</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Инсуффлятор Mindray HS-50F</t>
+          <t>Эндоскопический (лапароскопический) инсуффлятор</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mindray</t>
+          <t>подача CO₂ в брюшную полость при лапароскопии</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>эта категория</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Инсуффлятор Крыло КРИ 1003</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>Медицинский откашливатель (инсуффлятор-аспиратор)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>выведение мокроты из дыхательных путей</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>67299</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Инсуффлятор Крыло КРИ 1003П</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>67299</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Инсуффлятор Крыло КРИ 1003ПД</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>67299</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Газовый инсуффлятор MGB ML-G</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>MGB</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>от +10°С до +40°С</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Класс I, тип BF</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Газовый инсуффлятор MGB ML-GX</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>MGB</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>от +10°С до +40°С</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Класс I, тип BF</t>
+          <t>другая сущность, не путать</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3544,7 +3494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3870,12 +3820,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите профиль операций</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается инсуффляторы: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Сначала фиксируют, какие вмешательства планируются: общая лапароскопия, бариатрия, педиатрия, операции в забрюшинном пространстве. От этого зависит нужный набор режимов. Аппарат вроде Mindray HS-50F с бариатрическим, взрослым, детским и забрюшинным режимами подходит для смешанного потока; узкоспециализированному кабинету может хватить более простой модели.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3915,12 +3865,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Оцените диапазон и точность подачи</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Важны диапазон скорости подачи газа и её точность, особенно минимальные значения для деликатных и детских вмешательств: у Mindray HS-50F минимальная подача 0,1 л/мин. Плавная регулировка помогает поддерживать стабильное давление в полости. Требуемый диапазон согласуют с видами операций и возрастными группами пациентов.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3960,12 +3910,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Проверьте подогрев и отведение газа</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Страна производства, Производитель, Рабочая температура, Класс и тип безопасности. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Подогрев CO₂ снижает охлаждение тканей и запотевание оптики при длительных операциях, а функция отведения газа обеспечивает контролируемый выпуск дыма из полости. Эти функции есть, например, у Mindray HS-50F. Наличие подогрева и отведения оценивают исходя из продолжительности и типа вмешательств в кабинете.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4005,12 +3955,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Сверьте класс электробезопасности</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Mindray, MGB.</t>
+          <t>Для операционной важен класс электробезопасности и тип рабочей части: газовые инсуффляторы MGB ML-G и ML-GX относятся к классу I, тип BF. Соответствие требованиям электробезопасности — условие допуска в чистую зону. Класс и тип уточняют по паспорту конкретной модели до включения в комплект операционной.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4050,12 +4000,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Учтите управление и расходные магистрали</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Сенсорное управление и понятный интерфейс ускоряют настройку в ходе операции. Отдельно уточняют тип совместимых газовых магистралей и фильтров, их доступность и стоимость: это влияет на текущие расходы. Совместимость расходников с аппаратом проверяют заранее, чтобы избежать простоев из-за отсутствия нужных комплектующих.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -4095,12 +4045,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте регистрацию и сервис</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Для клинического применения инсуффлятор должен быть зарегистрированным медицинским изделием с действующим РУ Росздравнадзора. Заранее уточняют условия гарантии, доступность запчастей и сервис. Для аппарата, задействованного в операционном дне, важно, чтобы обслуживание и ремонт не приводили к длительной остановке работы.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -4150,7 +4100,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Инсуффляторы подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Mindray, MGB. При выборе обращают внимание на страна производства, производитель, рабочая температура, класс и тип безопасности, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Инсуффлятор выбирают под профиль операций и парк лапароскопических стоек. Подогрев газа и точная регулировка подачи важны там, где идут длительные вмешательства: холодный CO₂ охлаждает ткани и запотевает оптику. Наличие детского и бариатрического режимов расширяет применимость аппарата. Отдельно смотрят на класс электробезопасности и совместимость с расходными магистралями — это влияет и на безопасность, и на стоимость эксплуатации.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4434,13 +4384,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое инсуффляторы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Инсуффляторы — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Mindray, MGB. Подберём вариант под задачи вашего отделения.</t>
+          <t>Эндоскопический (лапароскопический) инсуффлятор — аппарат, подающий углекислый газ в брюшную полость, чтобы создать рабочее пространство (пневмоперитонеум) для лапароскопических операций. Его не следует путать с медицинским откашливателем: это разные устройства с разными задачами и конструкцией. При выборе учитывают режимы работы (взрослый, детский, бариатрический, забрюшинный), наличие подогрева и отведения газа, точность и диапазон подачи газа, класс электробезопасности, управление и совместимость с расходными магистралями. Модель Mindray HS-50F, например, поддерживает пять режимов, подогрев газа и минимальную подачу 0,1 л/мин.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4477,13 +4427,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Эндоскопические инсуффляторы: назначение</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Страна производства, Производитель, Рабочая температура, Класс и тип безопасности), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Эндоскопический инсуффлятор подаёт углекислый газ в брюшную полость и формирует пневмоперитонеум — рабочее пространство, необходимое для лапароскопических операций. Контролируемая подача поддерживает стабильное давление, обеспечивая хирургу обзор и доступ. Инсуффлятор входит в состав лапароскопической стойки и работает в связке с остальным оборудованием операционной.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4520,13 +4470,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Функции и режимы</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Инсуффляторы различаются набором режимов и функций. Модель Mindray HS-50F поддерживает взрослый, детский, бариатрический, забрюшинный и пользовательский режимы, оснащена подогревом и отведением газа, минимальная подача — 0,1 л/мин. Подогрев CO₂ снижает охлаждение тканей и запотевание оптики, отведение газа обеспечивает контролируемый выпуск дыма из полости.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4563,13 +4513,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Не путать с откашливателем</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>В выдаче по запросу «инсуффлятор» смешаны два разных устройства: лапароскопические инсуффляторы для подачи CO₂ в брюшную полость и медицинские откашливатели (инсуффляторы-аспираторы) для выведения мокроты. Это разные категории с разными задачами и конструкцией. В данном разделе представлены именно эндоскопические инсуффляторы для хирургии.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4586,6 +4536,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Выбор и безопасность</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>При выборе инсуффлятора учитывают профиль операций, набор режимов, диапазон и точность подачи газа, наличие подогрева и отведения, класс электробезопасности (например, класс I, тип BF у MGB ML-G) и совместимость с расходными магистралями. Для законной эксплуатации в клинике аппарат должен быть зарегистрированным медицинским изделием.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>insufflyatory</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
